--- a/Energy.xlsx
+++ b/Energy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Sectors\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55766C49-2840-483B-938F-DA4148A27373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87504D6E-65EB-4CDF-82D0-C1FE6C7567D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4680" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
+    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -689,16 +689,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -716,6 +708,26 @@
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -781,33 +793,39 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1268,1362 +1286,2976 @@
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="8"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="15"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="11">
         <f>+[1]Main!$J$2</f>
         <v>26.55</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <f>+[1]Main!$J$4*FX!C3</f>
         <v>1734017.1390000002</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <f>+([1]Main!$J$6-[1]Main!$J$5)*FX!C3</f>
         <v>21081.06</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="11">
         <f>+F4+G4</f>
         <v>1755098.1990000003</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12" t="s">
         <v>211</v>
       </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <f t="shared" ref="A6:A69" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="D16" s="5"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="D17" s="5"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="D18" s="5"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="D19" s="5"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="D20" s="5"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="D21" s="5"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="D22" s="5"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="D23" s="5"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="D24" s="5"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="D25" s="5"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="D26" s="5"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="D27" s="5"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="D28" s="5"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="D29" s="5"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="D30" s="5"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="D31" s="5"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="D32" s="5"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="D33" s="5"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="D34" s="5"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A35" s="10">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="D35" s="5"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="10">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="D36" s="5"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="D37" s="5"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="10">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="D38" s="5"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="10">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="D39" s="5"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A40" s="10">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="D40" s="5"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A41" s="10">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="D41" s="5"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A42" s="10">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="D42" s="5"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="5"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A43" s="10">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="D43" s="5"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A44" s="10">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="D44" s="5"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="D45" s="5"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="D46" s="5"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="10">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="D47" s="5"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="10">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="D48" s="5"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A49" s="10">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="D49" s="5"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A50" s="10">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="D50" s="5"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A51" s="10">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="D51" s="5"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A52" s="10">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="D52" s="5"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A53" s="10">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="D53" s="5"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A54" s="10">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="D54" s="5"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5"/>
+      <c r="T54" s="5"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="5"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A55" s="10">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="D55" s="5"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A56" s="10">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="D56" s="5"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A57" s="10">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="D57" s="5"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A58" s="10">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="D58" s="5"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="D59" s="5"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="D60" s="5"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="D61" s="5"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5"/>
+      <c r="W61" s="5"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="D62" s="5"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+      <c r="S62" s="5"/>
+      <c r="T62" s="5"/>
+      <c r="U62" s="5"/>
+      <c r="V62" s="5"/>
+      <c r="W62" s="5"/>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="D63" s="5"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="D64" s="5"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5"/>
+      <c r="S64" s="5"/>
+      <c r="T64" s="5"/>
+      <c r="U64" s="5"/>
+      <c r="V64" s="5"/>
+      <c r="W64" s="5"/>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="D65" s="5"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5"/>
+      <c r="W65" s="5"/>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="D66" s="5"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
+      <c r="U66" s="5"/>
+      <c r="V66" s="5"/>
+      <c r="W66" s="5"/>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="D67" s="5"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="5"/>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="D68" s="5"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+      <c r="S68" s="5"/>
+      <c r="T68" s="5"/>
+      <c r="U68" s="5"/>
+      <c r="V68" s="5"/>
+      <c r="W68" s="5"/>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="D69" s="5"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+      <c r="T69" s="5"/>
+      <c r="U69" s="5"/>
+      <c r="V69" s="5"/>
+      <c r="W69" s="5"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
         <f t="shared" ref="A70:A95" si="1">+A69+1</f>
         <v>67</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="D70" s="5"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+      <c r="R70" s="5"/>
+      <c r="S70" s="5"/>
+      <c r="T70" s="5"/>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5"/>
+      <c r="W70" s="5"/>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="D71" s="5"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="5"/>
+      <c r="R71" s="5"/>
+      <c r="S71" s="5"/>
+      <c r="T71" s="5"/>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5"/>
+      <c r="W71" s="5"/>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="D72" s="5"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+      <c r="S72" s="5"/>
+      <c r="T72" s="5"/>
+      <c r="U72" s="5"/>
+      <c r="V72" s="5"/>
+      <c r="W72" s="5"/>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+      <c r="S73" s="5"/>
+      <c r="T73" s="5"/>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5"/>
+      <c r="W73" s="5"/>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+      <c r="S74" s="5"/>
+      <c r="T74" s="5"/>
+      <c r="U74" s="5"/>
+      <c r="V74" s="5"/>
+      <c r="W74" s="5"/>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5"/>
+      <c r="W75" s="5"/>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="5"/>
+      <c r="R76" s="5"/>
+      <c r="S76" s="5"/>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+      <c r="V76" s="5"/>
+      <c r="W76" s="5"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A77" s="10">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+      <c r="S77" s="5"/>
+      <c r="T77" s="5"/>
+      <c r="U77" s="5"/>
+      <c r="V77" s="5"/>
+      <c r="W77" s="5"/>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A78" s="10">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="5"/>
+      <c r="R78" s="5"/>
+      <c r="S78" s="5"/>
+      <c r="T78" s="5"/>
+      <c r="U78" s="5"/>
+      <c r="V78" s="5"/>
+      <c r="W78" s="5"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+      <c r="S79" s="5"/>
+      <c r="T79" s="5"/>
+      <c r="U79" s="5"/>
+      <c r="V79" s="5"/>
+      <c r="W79" s="5"/>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A80" s="10">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="5"/>
+      <c r="R80" s="5"/>
+      <c r="S80" s="5"/>
+      <c r="T80" s="5"/>
+      <c r="U80" s="5"/>
+      <c r="V80" s="5"/>
+      <c r="W80" s="5"/>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A81" s="10">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5"/>
+      <c r="S81" s="5"/>
+      <c r="T81" s="5"/>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5"/>
+      <c r="W81" s="5"/>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A82" s="10">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="9"/>
-      <c r="G82" s="9"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="11"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="5"/>
+      <c r="R82" s="5"/>
+      <c r="S82" s="5"/>
+      <c r="T82" s="5"/>
+      <c r="U82" s="5"/>
+      <c r="V82" s="5"/>
+      <c r="W82" s="5"/>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A83" s="10">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9"/>
-      <c r="G83" s="9"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
+      <c r="R83" s="5"/>
+      <c r="S83" s="5"/>
+      <c r="T83" s="5"/>
+      <c r="U83" s="5"/>
+      <c r="V83" s="5"/>
+      <c r="W83" s="5"/>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A84" s="10">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+      <c r="K84" s="5"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="5"/>
+      <c r="R84" s="5"/>
+      <c r="S84" s="5"/>
+      <c r="T84" s="5"/>
+      <c r="U84" s="5"/>
+      <c r="V84" s="5"/>
+      <c r="W84" s="5"/>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A85" s="10">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="5"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+      <c r="Q85" s="5"/>
+      <c r="R85" s="5"/>
+      <c r="S85" s="5"/>
+      <c r="T85" s="5"/>
+      <c r="U85" s="5"/>
+      <c r="V85" s="5"/>
+      <c r="W85" s="5"/>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="9"/>
-      <c r="G86" s="9"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="5"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5"/>
+      <c r="Q86" s="5"/>
+      <c r="R86" s="5"/>
+      <c r="S86" s="5"/>
+      <c r="T86" s="5"/>
+      <c r="U86" s="5"/>
+      <c r="V86" s="5"/>
+      <c r="W86" s="5"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="9"/>
-      <c r="G87" s="9"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+      <c r="K87" s="5"/>
+      <c r="L87" s="5"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+      <c r="Q87" s="5"/>
+      <c r="R87" s="5"/>
+      <c r="S87" s="5"/>
+      <c r="T87" s="5"/>
+      <c r="U87" s="5"/>
+      <c r="V87" s="5"/>
+      <c r="W87" s="5"/>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="9"/>
-      <c r="G88" s="9"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
+      <c r="Q88" s="5"/>
+      <c r="R88" s="5"/>
+      <c r="S88" s="5"/>
+      <c r="T88" s="5"/>
+      <c r="U88" s="5"/>
+      <c r="V88" s="5"/>
+      <c r="W88" s="5"/>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A89" s="10">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="9"/>
-      <c r="G89" s="9"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+      <c r="Q89" s="5"/>
+      <c r="R89" s="5"/>
+      <c r="S89" s="5"/>
+      <c r="T89" s="5"/>
+      <c r="U89" s="5"/>
+      <c r="V89" s="5"/>
+      <c r="W89" s="5"/>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A90" s="10">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="11"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="5"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5"/>
+      <c r="Q90" s="5"/>
+      <c r="R90" s="5"/>
+      <c r="S90" s="5"/>
+      <c r="T90" s="5"/>
+      <c r="U90" s="5"/>
+      <c r="V90" s="5"/>
+      <c r="W90" s="5"/>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A91" s="10">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+      <c r="Q91" s="5"/>
+      <c r="R91" s="5"/>
+      <c r="S91" s="5"/>
+      <c r="T91" s="5"/>
+      <c r="U91" s="5"/>
+      <c r="V91" s="5"/>
+      <c r="W91" s="5"/>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="11"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+      <c r="Q92" s="5"/>
+      <c r="R92" s="5"/>
+      <c r="S92" s="5"/>
+      <c r="T92" s="5"/>
+      <c r="U92" s="5"/>
+      <c r="V92" s="5"/>
+      <c r="W92" s="5"/>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+      <c r="Q93" s="5"/>
+      <c r="R93" s="5"/>
+      <c r="S93" s="5"/>
+      <c r="T93" s="5"/>
+      <c r="U93" s="5"/>
+      <c r="V93" s="5"/>
+      <c r="W93" s="5"/>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
     </row>
     <row r="97" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
     </row>
     <row r="98" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
     </row>
     <row r="99" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
     </row>
     <row r="100" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
     </row>
     <row r="101" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
     </row>
     <row r="102" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E102" s="9"/>
-      <c r="F102" s="9"/>
-      <c r="G102" s="9"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2638,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E2C0E3F-CE32-4B66-A76D-5C7F8590B663}">
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2647,641 +4279,1995 @@
     <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
+      <c r="AI1" s="5"/>
+      <c r="AJ1" s="5"/>
+      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
+      <c r="AO1" s="5"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
+      <c r="AS1" s="5"/>
+      <c r="AT1" s="5"/>
+      <c r="AU1" s="5"/>
+      <c r="AV1" s="5"/>
+      <c r="AW1" s="5"/>
+      <c r="AX1" s="5"/>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
+      <c r="AL2" s="5"/>
+      <c r="AM2" s="5"/>
+      <c r="AN2" s="5"/>
+      <c r="AO2" s="5"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
+      <c r="AS2" s="5"/>
+      <c r="AT2" s="5"/>
+      <c r="AU2" s="5"/>
+      <c r="AV2" s="5"/>
+      <c r="AW2" s="5"/>
+      <c r="AX2" s="5"/>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="10"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="K3" s="8"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="5"/>
+      <c r="AK3" s="5"/>
+      <c r="AL3" s="5"/>
+      <c r="AM3" s="5"/>
+      <c r="AN3" s="5"/>
+      <c r="AO3" s="5"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
+      <c r="AS3" s="5"/>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="5"/>
+      <c r="AV3" s="5"/>
+      <c r="AW3" s="5"/>
+      <c r="AX3" s="5"/>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <f>+[2]Main!$I$2</f>
         <v>46.61</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <f>+[2]Main!$I$4</f>
         <v>20283.76646092</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="11">
         <f>+[2]Main!$I$6-[2]Main!$I$5</f>
         <v>1041.336</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="11">
         <f>+F4+G4</f>
         <v>21325.102460919999</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
+      <c r="AS4" s="5"/>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="5"/>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="E5" s="5"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="5"/>
+      <c r="AF5" s="5"/>
+      <c r="AG5" s="5"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="5"/>
+      <c r="AL5" s="5"/>
+      <c r="AM5" s="5"/>
+      <c r="AN5" s="5"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
+      <c r="AS5" s="5"/>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="5"/>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
         <f t="shared" ref="A6:A31" si="0">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="E6" s="5"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5"/>
+      <c r="AG6" s="5"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="5"/>
+      <c r="AL6" s="5"/>
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AR6" s="5"/>
+      <c r="AS6" s="5"/>
+      <c r="AT6" s="5"/>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="5"/>
+      <c r="AW6" s="5"/>
+      <c r="AX6" s="5"/>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="E7" s="5"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="5"/>
+      <c r="AM7" s="5"/>
+      <c r="AN7" s="5"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="5"/>
+      <c r="AS7" s="5"/>
+      <c r="AT7" s="5"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="5"/>
+      <c r="AX7" s="5"/>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="E8" s="5"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="5"/>
+      <c r="AF8" s="5"/>
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="5"/>
+      <c r="AL8" s="5"/>
+      <c r="AM8" s="5"/>
+      <c r="AN8" s="5"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="5"/>
+      <c r="AS8" s="5"/>
+      <c r="AT8" s="5"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="5"/>
+      <c r="AX8" s="5"/>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="E9" s="5"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="5"/>
+      <c r="AO9" s="5"/>
+      <c r="AP9" s="5"/>
+      <c r="AQ9" s="5"/>
+      <c r="AR9" s="5"/>
+      <c r="AS9" s="5"/>
+      <c r="AT9" s="5"/>
+      <c r="AU9" s="5"/>
+      <c r="AV9" s="5"/>
+      <c r="AW9" s="5"/>
+      <c r="AX9" s="5"/>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="E10" s="5"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="5"/>
+      <c r="AF10" s="5"/>
+      <c r="AG10" s="5"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="5"/>
+      <c r="AL10" s="5"/>
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="5"/>
+      <c r="AS10" s="5"/>
+      <c r="AT10" s="5"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="5"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="E11" s="5"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="5"/>
+      <c r="AF11" s="5"/>
+      <c r="AG11" s="5"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="5"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="5"/>
+      <c r="AL11" s="5"/>
+      <c r="AM11" s="5"/>
+      <c r="AN11" s="5"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="5"/>
+      <c r="AS11" s="5"/>
+      <c r="AT11" s="5"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="5"/>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="E12" s="5"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="5"/>
+      <c r="AF12" s="5"/>
+      <c r="AG12" s="5"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="5"/>
+      <c r="AL12" s="5"/>
+      <c r="AM12" s="5"/>
+      <c r="AN12" s="5"/>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="5"/>
+      <c r="AS12" s="5"/>
+      <c r="AT12" s="5"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="5"/>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <f>+[3]Main!$H$3</f>
         <v>11.26</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="11">
         <f>+[3]Main!$H$5</f>
         <v>2805.7720584200001</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="11">
         <f>+[3]Main!$H$7-[3]Main!$H$6</f>
         <v>-136.03399999999999</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="11">
         <f>+F13+G13</f>
         <v>2669.73805842</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5"/>
+      <c r="AG13" s="5"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="5"/>
+      <c r="AL13" s="5"/>
+      <c r="AM13" s="5"/>
+      <c r="AN13" s="5"/>
+      <c r="AO13" s="5"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+      <c r="AR13" s="5"/>
+      <c r="AS13" s="5"/>
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="5"/>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="E14" s="5"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
+      <c r="AH14" s="5"/>
+      <c r="AI14" s="5"/>
+      <c r="AJ14" s="5"/>
+      <c r="AK14" s="5"/>
+      <c r="AL14" s="5"/>
+      <c r="AM14" s="5"/>
+      <c r="AN14" s="5"/>
+      <c r="AO14" s="5"/>
+      <c r="AP14" s="5"/>
+      <c r="AQ14" s="5"/>
+      <c r="AR14" s="5"/>
+      <c r="AS14" s="5"/>
+      <c r="AT14" s="5"/>
+      <c r="AU14" s="5"/>
+      <c r="AV14" s="5"/>
+      <c r="AW14" s="5"/>
+      <c r="AX14" s="5"/>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="E15" s="5"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="5"/>
+      <c r="AI15" s="5"/>
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="5"/>
+      <c r="AL15" s="5"/>
+      <c r="AM15" s="5"/>
+      <c r="AN15" s="5"/>
+      <c r="AO15" s="5"/>
+      <c r="AP15" s="5"/>
+      <c r="AQ15" s="5"/>
+      <c r="AR15" s="5"/>
+      <c r="AS15" s="5"/>
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="5"/>
+      <c r="AV15" s="5"/>
+      <c r="AW15" s="5"/>
+      <c r="AX15" s="5"/>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="E16" s="5"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+      <c r="AE16" s="5"/>
+      <c r="AF16" s="5"/>
+      <c r="AG16" s="5"/>
+      <c r="AH16" s="5"/>
+      <c r="AI16" s="5"/>
+      <c r="AJ16" s="5"/>
+      <c r="AK16" s="5"/>
+      <c r="AL16" s="5"/>
+      <c r="AM16" s="5"/>
+      <c r="AN16" s="5"/>
+      <c r="AO16" s="5"/>
+      <c r="AP16" s="5"/>
+      <c r="AQ16" s="5"/>
+      <c r="AR16" s="5"/>
+      <c r="AS16" s="5"/>
+      <c r="AT16" s="5"/>
+      <c r="AU16" s="5"/>
+      <c r="AV16" s="5"/>
+      <c r="AW16" s="5"/>
+      <c r="AX16" s="5"/>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="E17" s="5"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5"/>
+      <c r="AG17" s="5"/>
+      <c r="AH17" s="5"/>
+      <c r="AI17" s="5"/>
+      <c r="AJ17" s="5"/>
+      <c r="AK17" s="5"/>
+      <c r="AL17" s="5"/>
+      <c r="AM17" s="5"/>
+      <c r="AN17" s="5"/>
+      <c r="AO17" s="5"/>
+      <c r="AP17" s="5"/>
+      <c r="AQ17" s="5"/>
+      <c r="AR17" s="5"/>
+      <c r="AS17" s="5"/>
+      <c r="AT17" s="5"/>
+      <c r="AU17" s="5"/>
+      <c r="AV17" s="5"/>
+      <c r="AW17" s="5"/>
+      <c r="AX17" s="5"/>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="E18" s="5"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
+      <c r="AS18" s="5"/>
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="5"/>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="E19" s="5"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5"/>
+      <c r="AG19" s="5"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="5"/>
+      <c r="AL19" s="5"/>
+      <c r="AM19" s="5"/>
+      <c r="AN19" s="5"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="5"/>
+      <c r="AS19" s="5"/>
+      <c r="AT19" s="5"/>
+      <c r="AU19" s="5"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="5"/>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="E20" s="5"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="5"/>
+      <c r="AF20" s="5"/>
+      <c r="AG20" s="5"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="5"/>
+      <c r="AL20" s="5"/>
+      <c r="AM20" s="5"/>
+      <c r="AN20" s="5"/>
+      <c r="AO20" s="5"/>
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="5"/>
+      <c r="AS20" s="5"/>
+      <c r="AT20" s="5"/>
+      <c r="AU20" s="5"/>
+      <c r="AV20" s="5"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="5"/>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A21" s="10">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="E21" s="5"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5"/>
+      <c r="AG21" s="5"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="5"/>
+      <c r="AL21" s="5"/>
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="5"/>
+      <c r="AO21" s="5"/>
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5"/>
+      <c r="AR21" s="5"/>
+      <c r="AS21" s="5"/>
+      <c r="AT21" s="5"/>
+      <c r="AU21" s="5"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="5"/>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="E22" s="5"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5"/>
+      <c r="AG22" s="5"/>
+      <c r="AH22" s="5"/>
+      <c r="AI22" s="5"/>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="5"/>
+      <c r="AL22" s="5"/>
+      <c r="AM22" s="5"/>
+      <c r="AN22" s="5"/>
+      <c r="AO22" s="5"/>
+      <c r="AP22" s="5"/>
+      <c r="AQ22" s="5"/>
+      <c r="AR22" s="5"/>
+      <c r="AS22" s="5"/>
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="5"/>
+      <c r="AV22" s="5"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="5"/>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="E23" s="5"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="5"/>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
+      <c r="AI23" s="5"/>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="5"/>
+      <c r="AL23" s="5"/>
+      <c r="AM23" s="5"/>
+      <c r="AN23" s="5"/>
+      <c r="AO23" s="5"/>
+      <c r="AP23" s="5"/>
+      <c r="AQ23" s="5"/>
+      <c r="AR23" s="5"/>
+      <c r="AS23" s="5"/>
+      <c r="AT23" s="5"/>
+      <c r="AU23" s="5"/>
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="5"/>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="E24" s="5"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="5"/>
+      <c r="AL24" s="5"/>
+      <c r="AM24" s="5"/>
+      <c r="AN24" s="5"/>
+      <c r="AO24" s="5"/>
+      <c r="AP24" s="5"/>
+      <c r="AQ24" s="5"/>
+      <c r="AR24" s="5"/>
+      <c r="AS24" s="5"/>
+      <c r="AT24" s="5"/>
+      <c r="AU24" s="5"/>
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="5"/>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A25" s="10">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="5"/>
+      <c r="AF25" s="5"/>
+      <c r="AG25" s="5"/>
+      <c r="AH25" s="5"/>
+      <c r="AI25" s="5"/>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="5"/>
+      <c r="AL25" s="5"/>
+      <c r="AM25" s="5"/>
+      <c r="AN25" s="5"/>
+      <c r="AO25" s="5"/>
+      <c r="AP25" s="5"/>
+      <c r="AQ25" s="5"/>
+      <c r="AR25" s="5"/>
+      <c r="AS25" s="5"/>
+      <c r="AT25" s="5"/>
+      <c r="AU25" s="5"/>
+      <c r="AV25" s="5"/>
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="5"/>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A26" s="10">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="5"/>
+      <c r="AG26" s="5"/>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="5"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="5"/>
+      <c r="AL26" s="5"/>
+      <c r="AM26" s="5"/>
+      <c r="AN26" s="5"/>
+      <c r="AO26" s="5"/>
+      <c r="AP26" s="5"/>
+      <c r="AQ26" s="5"/>
+      <c r="AR26" s="5"/>
+      <c r="AS26" s="5"/>
+      <c r="AT26" s="5"/>
+      <c r="AU26" s="5"/>
+      <c r="AV26" s="5"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="5"/>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+      <c r="AL27" s="5"/>
+      <c r="AM27" s="5"/>
+      <c r="AN27" s="5"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="5"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="5"/>
+      <c r="AS27" s="5"/>
+      <c r="AT27" s="5"/>
+      <c r="AU27" s="5"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="5"/>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="5"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5"/>
+      <c r="AI28" s="5"/>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="5"/>
+      <c r="AL28" s="5"/>
+      <c r="AM28" s="5"/>
+      <c r="AN28" s="5"/>
+      <c r="AO28" s="5"/>
+      <c r="AP28" s="5"/>
+      <c r="AQ28" s="5"/>
+      <c r="AR28" s="5"/>
+      <c r="AS28" s="5"/>
+      <c r="AT28" s="5"/>
+      <c r="AU28" s="5"/>
+      <c r="AV28" s="5"/>
+      <c r="AW28" s="5"/>
+      <c r="AX28" s="5"/>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="5"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AH29" s="5"/>
+      <c r="AI29" s="5"/>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="5"/>
+      <c r="AL29" s="5"/>
+      <c r="AM29" s="5"/>
+      <c r="AN29" s="5"/>
+      <c r="AO29" s="5"/>
+      <c r="AP29" s="5"/>
+      <c r="AQ29" s="5"/>
+      <c r="AR29" s="5"/>
+      <c r="AS29" s="5"/>
+      <c r="AT29" s="5"/>
+      <c r="AU29" s="5"/>
+      <c r="AV29" s="5"/>
+      <c r="AW29" s="5"/>
+      <c r="AX29" s="5"/>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="5"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="5"/>
+      <c r="AG30" s="5"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="5"/>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="5"/>
+      <c r="AL30" s="5"/>
+      <c r="AM30" s="5"/>
+      <c r="AN30" s="5"/>
+      <c r="AO30" s="5"/>
+      <c r="AP30" s="5"/>
+      <c r="AQ30" s="5"/>
+      <c r="AR30" s="5"/>
+      <c r="AS30" s="5"/>
+      <c r="AT30" s="5"/>
+      <c r="AU30" s="5"/>
+      <c r="AV30" s="5"/>
+      <c r="AW30" s="5"/>
+      <c r="AX30" s="5"/>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="5"/>
+      <c r="AE31" s="5"/>
+      <c r="AF31" s="5"/>
+      <c r="AG31" s="5"/>
+      <c r="AH31" s="5"/>
+      <c r="AI31" s="5"/>
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="5"/>
+      <c r="AL31" s="5"/>
+      <c r="AM31" s="5"/>
+      <c r="AN31" s="5"/>
+      <c r="AO31" s="5"/>
+      <c r="AP31" s="5"/>
+      <c r="AQ31" s="5"/>
+      <c r="AR31" s="5"/>
+      <c r="AS31" s="5"/>
+      <c r="AT31" s="5"/>
+      <c r="AU31" s="5"/>
+      <c r="AV31" s="5"/>
+      <c r="AW31" s="5"/>
+      <c r="AX31" s="5"/>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
     </row>
     <row r="33" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
     </row>
     <row r="34" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
     </row>
     <row r="35" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
     </row>
     <row r="36" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
     </row>
     <row r="37" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
     <row r="38" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
     </row>
     <row r="39" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
     </row>
     <row r="40" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row r="41" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
     </row>
     <row r="42" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
     </row>
     <row r="44" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
     </row>
     <row r="45" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
     </row>
     <row r="46" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
     </row>
     <row r="47" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
     <row r="48" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
     </row>
     <row r="50" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
     <row r="51" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
     </row>
     <row r="52" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
     <row r="53" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
     </row>
     <row r="54" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row r="55" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
     </row>
     <row r="56" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
     </row>
     <row r="57" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
     </row>
     <row r="58" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
     </row>
     <row r="59" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3295,43 +6281,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FADAB05-5D2F-4D8E-A6D3-5C6276016090}">
-  <dimension ref="B2:C5"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="5" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="5" t="s">
         <v>155</v>
       </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3340,33 +6430,73 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A405A685-6C08-484B-B8D8-1106B8517D54}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="5">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>0.71</v>
       </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Energy.xlsx
+++ b/Energy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9281520B-C477-410F-9589-903AA9881196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE1E89B-A5C1-4733-A27A-A3CDC02BA479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="213">
   <si>
     <t>Energy Universe</t>
   </si>
@@ -680,6 +681,9 @@
   </si>
   <si>
     <t>Q424</t>
+  </si>
+  <si>
+    <t>Q225</t>
   </si>
 </sst>
 </file>
@@ -689,13 +693,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -800,40 +810,43 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -966,6 +979,45 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>113.42</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>483537.47712182003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>14352</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>38989</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1293,7 +1345,7 @@
   <cols>
     <col min="1" max="1" width="3.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="28.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="4" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="4"/>
     <col min="5" max="5" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" style="4" bestFit="1" customWidth="1"/>
@@ -1448,12 +1500,12 @@
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1462,11 +1514,25 @@
       <c r="D5" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="E5" s="10">
+        <f>+[4]Main!$I$2</f>
+        <v>113.42</v>
+      </c>
+      <c r="F5" s="10">
+        <f>+[4]Main!$I$4</f>
+        <v>483537.47712182003</v>
+      </c>
+      <c r="G5" s="10">
+        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
+        <v>24637</v>
+      </c>
+      <c r="H5" s="10">
+        <f>+F5+G5</f>
+        <v>508174.47712182003</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>212</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -4273,6 +4339,7 @@
     <hyperlink ref="B11" r:id="rId2" xr:uid="{AB84B764-7B12-42DB-8C4E-3C6356264BBE}"/>
     <hyperlink ref="B12" r:id="rId3" xr:uid="{987BD4FB-3299-432C-915C-EDC5AA806DB1}"/>
     <hyperlink ref="B4" r:id="rId4" xr:uid="{A3430866-9D76-45B4-8B3F-8E09244FC54D}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{1E32A47A-D467-4EC8-813B-F6E3E28259A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Energy.xlsx
+++ b/Energy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64858B96-9B0B-4728-B179-2D72134E03C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84986ED3-DA52-4981-9AA3-BE401E6366E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="219">
   <si>
     <t>Energy Universe</t>
   </si>
@@ -713,13 +713,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="00000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -834,48 +840,49 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="defaultsheetstyle" xfId="2" xr:uid="{24F0CD60-3CC4-4E66-857F-2E640739A064}"/>
@@ -900,6 +907,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -939,6 +947,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -978,6 +987,47 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>121.3</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>105314.3582</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>10193</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5149</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -1012,11 +1062,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -1042,45 +1093,6 @@
         <row r="7">
           <cell r="H7">
             <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>121.3</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>105314.3582</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>10193</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>5149</v>
           </cell>
         </row>
       </sheetData>
@@ -1626,7 +1638,9 @@
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="20" t="s">
+        <v>164</v>
+      </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -3774,15 +3788,15 @@
         <v>216</v>
       </c>
       <c r="E73" s="9">
-        <f>+[5]Main!$J$2</f>
+        <f>+[3]Main!$J$2</f>
         <v>121.3</v>
       </c>
       <c r="F73" s="9">
-        <f>+[5]Main!$J$4*FX!C5</f>
+        <f>+[3]Main!$J$4*FX!C5</f>
         <v>123217.799094</v>
       </c>
       <c r="G73" s="9">
-        <f>+([5]Main!$J$6-[5]Main!$J$5)*FX!C5</f>
+        <f>+([3]Main!$J$6-[3]Main!$J$5)*FX!C5</f>
         <v>-5901.48</v>
       </c>
       <c r="H73" s="9">
@@ -4639,15 +4653,15 @@
         <v>158</v>
       </c>
       <c r="E4" s="2">
-        <f>+[3]Main!$I$2</f>
+        <f>+[4]Main!$I$2</f>
         <v>46.61</v>
       </c>
       <c r="F4" s="9">
-        <f>+[3]Main!$I$4</f>
+        <f>+[4]Main!$I$4</f>
         <v>20283.76646092</v>
       </c>
       <c r="G4" s="9">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
         <v>1041.336</v>
       </c>
       <c r="H4" s="9">
@@ -5202,15 +5216,15 @@
         <v>164</v>
       </c>
       <c r="E13" s="2">
-        <f>+[4]Main!$H$3</f>
+        <f>+[5]Main!$H$3</f>
         <v>11.26</v>
       </c>
       <c r="F13" s="9">
-        <f>+[4]Main!$H$5</f>
+        <f>+[5]Main!$H$5</f>
         <v>2805.7720584200001</v>
       </c>
       <c r="G13" s="9">
-        <f>+[4]Main!$H$7-[4]Main!$H$6</f>
+        <f>+[5]Main!$H$7-[5]Main!$H$6</f>
         <v>-136.03399999999999</v>
       </c>
       <c r="H13" s="9">

--- a/Energy.xlsx
+++ b/Energy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84986ED3-DA52-4981-9AA3-BE401E6366E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE5DC36-CA2B-4091-92B2-EE9D0087DD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{3927D63E-AF56-4894-AC80-59C624251D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="220">
   <si>
     <t>Energy Universe</t>
   </si>
@@ -703,6 +703,9 @@
   </si>
   <si>
     <t>EUR/USD</t>
+  </si>
+  <si>
+    <t>Reliance Industries</t>
   </si>
 </sst>
 </file>
@@ -713,13 +716,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="00000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -840,48 +849,49 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -3826,7 +3836,9 @@
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" s="21" t="s">
+        <v>219</v>
+      </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="9"/>
